--- a/AAII_Financials/Quarterly/RXRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="92">
   <si>
     <t>RXRX</t>
   </si>
@@ -656,116 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -781,64 +782,67 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E8" s="3">
         <v>6500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2500</v>
       </c>
       <c r="V8" s="3">
         <v>2500</v>
@@ -847,14 +851,14 @@
         <v>2500</v>
       </c>
       <c r="X8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Y8" s="3">
         <v>2600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,65 +874,68 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E9" s="3">
         <v>100400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>110200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>135700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>148800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>151500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>111100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>86700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>83100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>78700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>79400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>80900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>64400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>59100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,65 +966,68 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-93400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-93900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-74700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-130600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-129600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-136700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-106600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-60600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-68700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-64900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-68500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-70400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-53400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-2200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-6500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-2500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1048,8 +1058,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1081,80 +1094,81 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E12" s="3">
         <v>87900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>95900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>121100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>128600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>129600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>98300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>74600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>73900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>69500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>70000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>55100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>46700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>40800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>38400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>46000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>33200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>29500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>24000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13200</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,8 +1184,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,28 +1276,31 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-8500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>6000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -1291,39 +1311,39 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>800</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,8 +1359,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1348,55 +1368,58 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E15" s="3">
         <v>19700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>23800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>7600</v>
       </c>
       <c r="N15" s="3">
         <v>7600</v>
       </c>
       <c r="O15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="P15" s="3">
         <v>5500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>200</v>
-      </c>
-      <c r="R15" s="3">
-        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>100</v>
@@ -1416,8 +1439,8 @@
       <c r="X15" s="3">
         <v>100</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
+      <c r="Y15" s="3">
+        <v>100</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
@@ -1437,8 +1460,11 @@
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1467,80 +1493,81 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E17" s="3">
         <v>135000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>152400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>177400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>195500</v>
       </c>
-      <c r="H17" s="3">
-        <v>206100</v>
-      </c>
       <c r="I17" s="3">
+        <v>200200</v>
+      </c>
+      <c r="J17" s="3">
         <v>188300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>124400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>115000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>110100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>111000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>110100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>92700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>80800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>74700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>75700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>73900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>61300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>49800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>33000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18400</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1556,80 +1583,83 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-128500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-116900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-172200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-176200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-191400</v>
-      </c>
       <c r="I18" s="3">
+        <v>-185400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-183800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-98400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-96300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-99600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-81700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-68700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-61000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-62500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-66200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-56000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-65000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-47300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-41000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,8 +1675,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1678,64 +1711,65 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>16300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
@@ -1744,14 +1778,14 @@
         <v>100</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,77 +1801,80 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-117800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-108000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-103400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-145900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-153000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-188400</v>
-      </c>
       <c r="I21" s="3">
+        <v>-182400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-170000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-91800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-92000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-88800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-95200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-90400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-76100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-65100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-54300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-57400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-62800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-53200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-62700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-44800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-38600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-29100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1856,38 +1893,41 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>500</v>
       </c>
       <c r="H22" s="3">
         <v>500</v>
       </c>
       <c r="I22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J22" s="3">
         <v>600</v>
       </c>
       <c r="K22" s="3">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1912,24 +1952,24 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,80 +1985,83 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-122100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-108100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-162300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-171900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-202600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-178900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-95700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-98100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-92200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-97100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-93000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-76700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-57500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-60400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-65600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-56000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-64900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-47400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-43400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2034,44 +2077,47 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4600</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2087,8 +2133,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2123,8 +2169,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2212,80 +2261,83 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-117500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-108100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-162300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-171900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-202500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-178900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-95800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-97500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-91400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-93000</v>
       </c>
       <c r="N26" s="3">
         <v>-93000</v>
       </c>
       <c r="O26" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="P26" s="3">
         <v>-76700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-57500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-60400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-65600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-56000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-64900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-47400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-43400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2301,80 +2353,83 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-117500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-108100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-162300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-171900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-202500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-178900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-95800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-97500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-91400</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-93000</v>
       </c>
       <c r="N27" s="3">
         <v>-93000</v>
       </c>
       <c r="O27" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="P27" s="3">
         <v>-76700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-57500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-60400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-65600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-56000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-64900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-47400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-43400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2390,8 +2445,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2479,8 +2537,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2568,8 +2629,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2657,8 +2721,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2746,64 +2813,67 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-16300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
@@ -2812,14 +2882,14 @@
         <v>-100</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,80 +2905,83 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-117500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-108100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-162300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-171900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-202500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-178900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-95800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-97500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-91400</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-93000</v>
       </c>
       <c r="N33" s="3">
         <v>-93000</v>
       </c>
       <c r="O33" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="P33" s="3">
         <v>-76700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-57500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-60400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-65600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-56000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-64900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-47400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-43400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,8 +2997,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3013,80 +3089,83 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-117500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-108100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-162300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-171900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-202500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-178900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-95800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-97500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-91400</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-93000</v>
       </c>
       <c r="N35" s="3">
         <v>-93000</v>
       </c>
       <c r="O35" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="P35" s="3">
         <v>-76700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-57500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-60400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-65600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-56000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-64900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-47400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-43400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3102,85 +3181,88 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3278,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3229,8 +3314,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3262,77 +3348,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>545700</v>
+      </c>
+      <c r="E41" s="3">
         <v>654500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>743300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>659800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>525100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>500500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>594400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>427600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>474300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>296300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>391600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>387300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>405900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>473100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>549900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>454600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>453900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>507900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>285100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>394700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>632700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>214100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3438,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3402,20 +3492,20 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>61600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>83200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>231400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>184200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3431,8 +3521,8 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3440,77 +3530,80 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E43" s="3">
         <v>13600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2300</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,8 +3622,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3573,8 +3669,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3618,77 +3714,80 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E45" s="3">
         <v>24200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>43700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>41500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7700</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3707,77 +3806,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>603500</v>
+      </c>
+      <c r="E46" s="3">
         <v>709600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>812800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>714100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>587200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>584100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>714300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>474200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>522400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>343600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>438100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>410500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>431000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>492100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>569800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>481600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>546000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>619500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>534700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>600900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>647600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>221800</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,16 +3898,19 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>4400</v>
-      </c>
-      <c r="E47" s="3">
-        <v>4400</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>4400</v>
@@ -3816,8 +3921,8 @@
       <c r="H47" s="3">
         <v>4400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+      <c r="I47" s="3">
+        <v>4400</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -3840,8 +3945,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3885,77 +3990,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E48" s="3">
         <v>157300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>169500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>181200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>193600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>204800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>233200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>159200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>156300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>122200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>120200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>120300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>124700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>125100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>121400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>119500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>116200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>104000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>55400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>48500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>44600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3974,77 +4082,80 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>443200</v>
+      </c>
+      <c r="E49" s="3">
         <v>454200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>472100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>484400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>505600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>493900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>484700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>86100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>90300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>85100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>88500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>92200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>103300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>2100</v>
       </c>
       <c r="Q49" s="3">
         <v>2100</v>
       </c>
       <c r="R49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S49" s="3">
         <v>2300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2200</v>
-      </c>
-      <c r="V49" s="3">
-        <v>2300</v>
       </c>
       <c r="W49" s="3">
         <v>2300</v>
       </c>
       <c r="X49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Y49" s="3">
         <v>2400</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4063,8 +4174,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4152,8 +4266,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4241,34 +4358,37 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13000</v>
+        <v>17900</v>
       </c>
       <c r="E52" s="3">
-        <v>14400</v>
+        <v>17400</v>
       </c>
       <c r="F52" s="3">
         <v>14400</v>
       </c>
       <c r="G52" s="3">
+        <v>14400</v>
+      </c>
+      <c r="H52" s="3">
         <v>10600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>6900</v>
       </c>
       <c r="L52" s="3">
         <v>6900</v>
@@ -4277,41 +4397,41 @@
         <v>6900</v>
       </c>
       <c r="N52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O52" s="3">
         <v>7800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8300</v>
-      </c>
-      <c r="T52" s="3">
-        <v>8700</v>
       </c>
       <c r="U52" s="3">
         <v>8700</v>
       </c>
       <c r="V52" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4330,8 +4450,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4419,77 +4542,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1212700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1339500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1474100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1399500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1302400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1305200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1448600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>726500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>775900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>557800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>653700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>630800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>666700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>627400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>701300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>611500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>672500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>734300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>610300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>658600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>698600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>271900</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4508,8 +4634,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4541,8 +4670,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4574,77 +4704,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E57" s="3">
         <v>20300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>25100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,52 +4794,55 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E58" s="3">
         <v>22400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>22200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
@@ -4726,14 +4860,14 @@
         <v>100</v>
       </c>
       <c r="W58" s="3">
+        <v>100</v>
+      </c>
+      <c r="X58" s="3">
         <v>3100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4752,77 +4886,80 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E59" s="3">
         <v>33800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>63400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>37800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>73100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>57800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>79100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>93400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>81500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>43700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4841,77 +4978,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E60" s="3">
         <v>129700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>147700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>155100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>164000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>142000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>187500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>108900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>86100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>73900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>93200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>94100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>114000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>92200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>83000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>96700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>85700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>46700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>42900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4930,55 +5070,58 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E61" s="3">
         <v>50000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>67600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>72500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>86300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>74200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>44500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>500</v>
-      </c>
-      <c r="R61" s="3">
-        <v>600</v>
       </c>
       <c r="S61" s="3">
         <v>600</v>
@@ -4990,17 +5133,17 @@
         <v>600</v>
       </c>
       <c r="V61" s="3">
+        <v>600</v>
+      </c>
+      <c r="W61" s="3">
         <v>700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5019,37 +5162,40 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3000</v>
       </c>
       <c r="K62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>3000</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -5063,33 +5209,33 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>114700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>139900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>137700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>154400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5108,8 +5254,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5197,8 +5346,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5286,8 +5438,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5375,77 +5530,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>297700</v>
+      </c>
+      <c r="E66" s="3">
         <v>314800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>343300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>352600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>383200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>371300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>413800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>201900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>191400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>156700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>190300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>192900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>197700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>197200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>215500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>223500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>234900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>240800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>67400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>56700</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5464,8 +5622,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5497,8 +5658,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5586,8 +5748,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5675,8 +5840,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5741,11 +5909,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>448300</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5764,8 +5932,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5853,77 +6024,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2324500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2193500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2076000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1967900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1805600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1633700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1431300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1252400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1156500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1059000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-967600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-874600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-781600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-704900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-639600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-582100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-521600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-456100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-400100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-335100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-287700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-244300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5942,8 +6116,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6031,8 +6208,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6120,8 +6300,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6209,77 +6392,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>915000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1024800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1130900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1046900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>919100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>933900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1034800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>524600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>584400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>401200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>463400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>438000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>469000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>430200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>485800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>388000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>437600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>493600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>542900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>599000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>642700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-233000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6298,8 +6484,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6387,85 +6576,88 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6481,80 +6673,83 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-117500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-108100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-162300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-171900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-202500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-178900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-95800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-97500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-91400</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-93000</v>
       </c>
       <c r="N81" s="3">
         <v>-93000</v>
       </c>
       <c r="O81" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="P81" s="3">
         <v>-76700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-57500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-60400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-65600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-56000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-64900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-47400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-43400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6765,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6603,77 +6801,78 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E83" s="3">
         <v>7600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4200</v>
       </c>
       <c r="J83" s="3">
         <v>4200</v>
       </c>
       <c r="K83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L83" s="3">
         <v>4000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2900</v>
-      </c>
-      <c r="O83" s="3">
-        <v>2700</v>
       </c>
       <c r="P83" s="3">
         <v>2700</v>
       </c>
       <c r="Q83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="R83" s="3">
         <v>3200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>2800</v>
       </c>
       <c r="T83" s="3">
         <v>2800</v>
       </c>
       <c r="U83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V83" s="3">
         <v>2200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6692,8 +6891,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6781,8 +6983,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6870,8 +7075,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6959,8 +7167,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7048,8 +7259,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7137,77 +7351,80 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-81100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-46100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-117400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-76400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-132000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-115400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-59200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-82200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-102300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-74100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-72900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-67500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-44700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-54500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-61600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>77400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-61200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-33000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-33700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-30800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7226,8 +7443,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7259,77 +7479,78 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,8 +7569,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7437,8 +7661,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7526,77 +7753,80 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>275500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>53000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>143300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-52200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-193900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7615,8 +7845,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7648,8 +7881,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7692,8 +7926,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7737,8 +7971,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7826,8 +8063,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7915,8 +8155,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8004,77 +8247,80 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>132000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>251300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>97700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>40500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>263100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>80700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>53800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>147300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>463700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8093,44 +8339,47 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E101" s="3">
         <v>4800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -8155,8 +8404,8 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -8182,77 +8431,80 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-108400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-88700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>86800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>133300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>24700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-93900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>167200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-46900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>176600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-95300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-65600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-76700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>94200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-54000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>222800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-109600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-238000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>423800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8269,6 +8521,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
